--- a/converted_files/837/prof-encounter.xlsx
+++ b/converted_files/837/prof-encounter.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4d0d</t>
+          <t>69e82c69836d7d05c9a0548f</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4d0d</t>
+          <t>69e82c69836d7d05c9a0548f</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4d0d</t>
+          <t>69e82c69836d7d05c9a0548f</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4d0d</t>
+          <t>69e82c69836d7d05c9a0548f</t>
         </is>
       </c>
       <c r="B5"/>

--- a/converted_files/837/prof-encounter.xlsx
+++ b/converted_files/837/prof-encounter.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4d0d</t>
+          <t>69efef05ad4799caa7f5e142</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4d0d</t>
+          <t>69efef05ad4799caa7f5e142</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4d0d</t>
+          <t>69efef05ad4799caa7f5e142</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4d0d</t>
+          <t>69efef05ad4799caa7f5e142</t>
         </is>
       </c>
       <c r="B5"/>

--- a/converted_files/837/prof-encounter.xlsx
+++ b/converted_files/837/prof-encounter.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0548f</t>
+          <t>6a04cb3b618f76c4f7b19340</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0548f</t>
+          <t>6a04cb3b618f76c4f7b19340</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0548f</t>
+          <t>6a04cb3b618f76c4f7b19340</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0548f</t>
+          <t>6a04cb3b618f76c4f7b19340</t>
         </is>
       </c>
       <c r="B5"/>

--- a/converted_files/837/prof-encounter.xlsx
+++ b/converted_files/837/prof-encounter.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3b618f76c4f7b19340</t>
+          <t>6a04cc5b1ef26d534baf3e87</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3b618f76c4f7b19340</t>
+          <t>6a04cc5b1ef26d534baf3e87</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3b618f76c4f7b19340</t>
+          <t>6a04cc5b1ef26d534baf3e87</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3b618f76c4f7b19340</t>
+          <t>6a04cc5b1ef26d534baf3e87</t>
         </is>
       </c>
       <c r="B5"/>

--- a/converted_files/837/prof-encounter.xlsx
+++ b/converted_files/837/prof-encounter.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5b1ef26d534baf3e87</t>
+          <t>6a0614def8d6a2fc74348cd5</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5b1ef26d534baf3e87</t>
+          <t>6a0614def8d6a2fc74348cd5</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5b1ef26d534baf3e87</t>
+          <t>6a0614def8d6a2fc74348cd5</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5b1ef26d534baf3e87</t>
+          <t>6a0614def8d6a2fc74348cd5</t>
         </is>
       </c>
       <c r="B5"/>

--- a/converted_files/837/prof-encounter.xlsx
+++ b/converted_files/837/prof-encounter.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348cd5</t>
+          <t>6a32cb6497613a0e499093a0</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348cd5</t>
+          <t>6a32cb6497613a0e499093a0</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348cd5</t>
+          <t>6a32cb6497613a0e499093a0</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348cd5</t>
+          <t>6a32cb6497613a0e499093a0</t>
         </is>
       </c>
       <c r="B5"/>
